--- a/Result/profitability/2478.xlsx
+++ b/Result/profitability/2478.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.745</v>
+        <v>0.91625</v>
       </c>
       <c r="N2" t="n">
-        <v>22.56375</v>
+        <v>23.90875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7612500000000001</v>
+        <v>0.8675</v>
       </c>
       <c r="N3" t="n">
-        <v>24.2775</v>
+        <v>25.64125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>0.71875</v>
+        <v>0.83</v>
       </c>
       <c r="N4" t="n">
-        <v>26.35125</v>
+        <v>27.1775</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5962499999999999</v>
+        <v>0.7412500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>27.08625</v>
+        <v>27.9525</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.54125</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>26.87375</v>
+        <v>27.5625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.46125</v>
+        <v>0.56875</v>
       </c>
       <c r="N7" t="n">
-        <v>27.68375</v>
+        <v>28.23625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>0.44625</v>
+        <v>0.525</v>
       </c>
       <c r="N8" t="n">
-        <v>29.3325</v>
+        <v>29.7925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1710</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1219</v>
+      </c>
+      <c r="E75" t="n">
+        <v>491</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>313</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.28%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="J75" t="n">
+        <v>286</v>
+      </c>
+      <c r="K75" t="n">
+        <v>252</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.5875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6300000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5526315789473686</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1471411435425829</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.901639344262295</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3184742647058822</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
